--- a/website/immunizations-measles/StructureDefinition-IMMZD1ClientHistoryMeasles.xlsx
+++ b/website/immunizations-measles/StructureDefinition-IMMZD1ClientHistoryMeasles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-25T09:50:10+00:00</t>
+    <t>2023-12-26T06:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/website/immunizations-measles/StructureDefinition-IMMZD1ClientHistoryMeasles.xlsx
+++ b/website/immunizations-measles/StructureDefinition-IMMZD1ClientHistoryMeasles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-26T06:33:44+00:00</t>
+    <t>2023-12-26T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
